--- a/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-22T16:12:30+00:00</t>
+    <t>2025-05-26T06:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-26T06:59:47+00:00</t>
+    <t>2025-06-02T15:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T15:02:23+00:00</t>
+    <t>2025-10-22T09:09:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-22T09:09:51+00:00</t>
+    <t>2025-10-28T10:00:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-28T10:00:18+00:00</t>
+    <t>2025-11-19T09:47:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-19T09:47:12+00:00</t>
+    <t>2026-01-14T12:51:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T12:51:21+00:00</t>
+    <t>2026-02-24T09:27:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -119,6 +120,9 @@
   </si>
   <si>
     <t>http://hl7.fr/fhir/fr/preadmission/CodeSystem/document-type-cs</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J66-TypeCode-DMP/FHIR/JDV-J66-TypeCode-DMP</t>
   </si>
 </sst>
 </file>
@@ -466,4 +470,44 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
+++ b/nmoreau/ig/ValueSet-preadmission-document-type-vs.xlsx
@@ -9,13 +9,13 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include ValueSet #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -50,7 +50,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T09:27:09+00:00</t>
+    <t>2026-04-10T11:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>http://hl7.fr/fhir/fr/preadmission/CodeSystem/document-type-cs</t>
+  </si>
+  <si>
+    <t>ValueSet URL</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J66-TypeCode-DMP/FHIR/JDV-J66-TypeCode-DMP</t>
@@ -474,7 +477,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -483,28 +486,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
